--- a/Liste_Anforderungen.xlsx
+++ b/Liste_Anforderungen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fhaachen-my.sharepoint.com/personal/lk3815s_ad_fh-aachen_de/Documents/FH Aachen/3. Semester/SWE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02F8A414-7F53-4394-AE29-06C0EEA62C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{02F8A414-7F53-4394-AE29-06C0EEA62C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{749ABC8E-2262-4A0A-B99F-A09CCF630EBA}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" xr2:uid="{AC51961E-5C48-4807-BF72-91486C1696AE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{AC51961E-5C48-4807-BF72-91486C1696AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>Anforderung / Idee</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Dashboard mit Fächer-Auswahl</t>
   </si>
   <si>
-    <t>Einzelne Themenseiten zu Fächern</t>
-  </si>
-  <si>
     <t>Login für Lehrer zum hochladen von PDFs</t>
   </si>
   <si>
@@ -63,12 +60,6 @@
     <t>27.11.-18.12.2025</t>
   </si>
   <si>
-    <t>23.10.-13.11.2025</t>
-  </si>
-  <si>
-    <t>13.11.-27.11.2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">Forum für Fragen und </t>
   </si>
   <si>
@@ -82,6 +73,66 @@
   </si>
   <si>
     <t>Optional / je nach Zeit:</t>
+  </si>
+  <si>
+    <t>06.11.-27.11.2025</t>
+  </si>
+  <si>
+    <t>Verantwortlicher</t>
+  </si>
+  <si>
+    <t>Salma, Safa</t>
+  </si>
+  <si>
+    <t>Mathe</t>
+  </si>
+  <si>
+    <t>Deutsch</t>
+  </si>
+  <si>
+    <t>Englisch</t>
+  </si>
+  <si>
+    <t>Biologie</t>
+  </si>
+  <si>
+    <t>Einzelne Themenseiten zu Fächern (Layout)</t>
+  </si>
+  <si>
+    <t>Erdkunde</t>
+  </si>
+  <si>
+    <t>Geschichte</t>
+  </si>
+  <si>
+    <t>Musik</t>
+  </si>
+  <si>
+    <t>Kunst</t>
+  </si>
+  <si>
+    <t>Religion</t>
+  </si>
+  <si>
+    <t>Lennart</t>
+  </si>
+  <si>
+    <t>Zakaria</t>
+  </si>
+  <si>
+    <t>Salma</t>
+  </si>
+  <si>
+    <t>Mannmeet</t>
+  </si>
+  <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
+    <t>zugehörig zu Fächern</t>
+  </si>
+  <si>
+    <t>Roman</t>
   </si>
 </sst>
 </file>
@@ -143,9 +194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -183,7 +234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -289,7 +340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -431,7 +482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -439,119 +490,201 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84406A77-DF62-445A-B012-FB37D1D06365}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="41.140625" customWidth="1"/>
+    <col min="1" max="1" width="41.1328125" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Liste_Anforderungen.xlsx
+++ b/Liste_Anforderungen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fhaachen-my.sharepoint.com/personal/lk3815s_ad_fh-aachen_de/Documents/FH Aachen/3. Semester/SWE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{02F8A414-7F53-4394-AE29-06C0EEA62C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{749ABC8E-2262-4A0A-B99F-A09CCF630EBA}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{02F8A414-7F53-4394-AE29-06C0EEA62C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D448E57-651F-4247-8BB0-ADFA5DC51D6A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{AC51961E-5C48-4807-BF72-91486C1696AE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Anforderung / Idee</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Übungsblätter über PDF-Viewer ansehen</t>
   </si>
   <si>
-    <t>Dashboard mit Fächer-Auswahl</t>
-  </si>
-  <si>
     <t>Login für Lehrer zum hochladen von PDFs</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>27.11.-18.12.2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Forum für Fragen und </t>
-  </si>
-  <si>
     <t>Verlinken von Youtube-Lernvideos</t>
   </si>
   <si>
@@ -81,9 +75,6 @@
     <t>Verantwortlicher</t>
   </si>
   <si>
-    <t>Salma, Safa</t>
-  </si>
-  <si>
     <t>Mathe</t>
   </si>
   <si>
@@ -99,21 +90,12 @@
     <t>Einzelne Themenseiten zu Fächern (Layout)</t>
   </si>
   <si>
-    <t>Erdkunde</t>
-  </si>
-  <si>
     <t>Geschichte</t>
   </si>
   <si>
     <t>Musik</t>
   </si>
   <si>
-    <t>Kunst</t>
-  </si>
-  <si>
-    <t>Religion</t>
-  </si>
-  <si>
     <t>Lennart</t>
   </si>
   <si>
@@ -126,13 +108,22 @@
     <t>Mannmeet</t>
   </si>
   <si>
-    <t>Sebastian</t>
-  </si>
-  <si>
     <t>zugehörig zu Fächern</t>
   </si>
   <si>
     <t>Roman</t>
+  </si>
+  <si>
+    <t>E-Test Funktion</t>
+  </si>
+  <si>
+    <t>Forum für Fragen</t>
+  </si>
+  <si>
+    <t>Dashboard mit Fach-Dashboard</t>
+  </si>
+  <si>
+    <t>Safa</t>
   </si>
 </sst>
 </file>
@@ -191,6 +182,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -490,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84406A77-DF62-445A-B012-FB37D1D06365}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="41.1328125" customWidth="1"/>
@@ -506,58 +501,58 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -565,126 +560,116 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>12</v>
       </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
